--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Front_Summary.xlsx
@@ -434,12 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -451,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.4731</v>
+        <v>17.58334</v>
       </c>
       <c r="D2" t="n">
-        <v>16.71961</v>
+        <v>17.03736</v>
       </c>
       <c r="E2" t="n">
-        <v>16.97228</v>
+        <v>17.22311</v>
       </c>
       <c r="F2" t="n">
-        <v>23.01962</v>
+        <v>44.02522</v>
       </c>
       <c r="G2" t="n">
-        <v>35.17244</v>
+        <v>0.05344</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.88807</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.54393</v>
+        <v>17.92905</v>
       </c>
       <c r="D3" t="n">
-        <v>16.88993</v>
+        <v>17.36467</v>
       </c>
       <c r="E3" t="n">
-        <v>17.35913</v>
+        <v>17.54508</v>
       </c>
       <c r="F3" t="n">
-        <v>22.98323</v>
+        <v>44.47698</v>
       </c>
       <c r="G3" t="n">
-        <v>35.83936</v>
+        <v>0.05291</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.88581</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.08284</v>
+        <v>17.77329</v>
       </c>
       <c r="D4" t="n">
-        <v>16.38511</v>
+        <v>17.06592</v>
       </c>
       <c r="E4" t="n">
-        <v>17.11812</v>
+        <v>17.54393</v>
       </c>
       <c r="F4" t="n">
-        <v>22.73616</v>
+        <v>44.89729</v>
       </c>
       <c r="G4" t="n">
-        <v>36.33564</v>
+        <v>0.05358</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.92418</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.67052</v>
+        <v>17.60158</v>
       </c>
       <c r="D5" t="n">
-        <v>16.8097</v>
+        <v>16.9793</v>
       </c>
       <c r="E5" t="n">
-        <v>16.76221</v>
+        <v>17.11104</v>
       </c>
       <c r="F5" t="n">
-        <v>22.69834</v>
+        <v>44.3803</v>
       </c>
       <c r="G5" t="n">
-        <v>35.97353</v>
+        <v>0.05287</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.93503</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.63453</v>
+        <v>17.77761</v>
       </c>
       <c r="D6" t="n">
-        <v>16.99279</v>
+        <v>17.07262</v>
       </c>
       <c r="E6" t="n">
-        <v>17.05096</v>
+        <v>17.44804</v>
       </c>
       <c r="F6" t="n">
-        <v>22.73991</v>
+        <v>44.34094</v>
       </c>
       <c r="G6" t="n">
-        <v>35.86761</v>
+        <v>0.05322</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.92377</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.09597</v>
+        <v>17.85319</v>
       </c>
       <c r="D7" t="n">
-        <v>16.54054</v>
+        <v>17.26146</v>
       </c>
       <c r="E7" t="n">
-        <v>17.16096</v>
+        <v>17.45156</v>
       </c>
       <c r="F7" t="n">
-        <v>22.97088</v>
+        <v>44.56922</v>
       </c>
       <c r="G7" t="n">
-        <v>36.0888</v>
+        <v>0.05181</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.88437</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.53491</v>
+        <v>17.61731</v>
       </c>
       <c r="D8" t="n">
-        <v>16.68949</v>
+        <v>17.52197</v>
       </c>
       <c r="E8" t="n">
-        <v>16.94899</v>
+        <v>17.58468</v>
       </c>
       <c r="F8" t="n">
-        <v>22.28971</v>
+        <v>44.63433</v>
       </c>
       <c r="G8" t="n">
-        <v>35.73143</v>
+        <v>0.05281</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.88322</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>17.33714</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17.20973</v>
+      </c>
+      <c r="E9" t="n">
         <v>17.29781</v>
       </c>
-      <c r="D9" t="n">
-        <v>16.83277</v>
-      </c>
-      <c r="E9" t="n">
-        <v>17.41702</v>
-      </c>
       <c r="F9" t="n">
-        <v>22.87018</v>
+        <v>44.74533</v>
       </c>
       <c r="G9" t="n">
-        <v>35.47295</v>
+        <v>0.05376</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.91471</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.24145</v>
+        <v>17.65337</v>
       </c>
       <c r="D10" t="n">
-        <v>16.90444</v>
+        <v>17.13696</v>
       </c>
       <c r="E10" t="n">
-        <v>17.23266</v>
+        <v>17.42163</v>
       </c>
       <c r="F10" t="n">
-        <v>22.27078</v>
+        <v>44.67728</v>
       </c>
       <c r="G10" t="n">
-        <v>35.41308</v>
+        <v>0.05179</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.8859</v>
       </c>
     </row>
     <row r="11">
@@ -664,17 +696,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -686,26 +713,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>17.29909</v>
-      </c>
-      <c r="D12" t="n">
-        <v>17.5051</v>
-      </c>
-      <c r="E12" t="n">
-        <v>17.48567</v>
-      </c>
-      <c r="F12" t="n">
-        <v>45.02667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0542</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.85538</v>
+          <t>Trace 1</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -714,24 +723,6 @@
           <t>Unit 8</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>17.66875</v>
-      </c>
-      <c r="D13" t="n">
-        <v>17.07865</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.61308</v>
-      </c>
-      <c r="F13" t="n">
-        <v>44.28437</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05372</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.92882</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -739,24 +730,6 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>17.47831</v>
-      </c>
-      <c r="D14" t="n">
-        <v>17.10197</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.62278</v>
-      </c>
-      <c r="F14" t="n">
-        <v>44.72764</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05322</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.89924</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -764,24 +737,6 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>18.18476</v>
-      </c>
-      <c r="D15" t="n">
-        <v>17.578</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17.67813</v>
-      </c>
-      <c r="F15" t="n">
-        <v>44.48878</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05228</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.92395</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -789,24 +744,6 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>17.86383</v>
-      </c>
-      <c r="D16" t="n">
-        <v>17.52913</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.58194</v>
-      </c>
-      <c r="F16" t="n">
-        <v>43.78858</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05313</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.91007</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -814,24 +751,6 @@
           <t>Unit 6</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>17.73829</v>
-      </c>
-      <c r="D17" t="n">
-        <v>17.74266</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17.33968</v>
-      </c>
-      <c r="F17" t="n">
-        <v>44.62149</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0529</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.92868</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -839,24 +758,6 @@
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>17.33578</v>
-      </c>
-      <c r="D18" t="n">
-        <v>17.39908</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.36182</v>
-      </c>
-      <c r="F18" t="n">
-        <v>44.99017</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05365</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.95058</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -864,24 +765,6 @@
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>17.8706</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17.57583</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.45307</v>
-      </c>
-      <c r="F19" t="n">
-        <v>45.3109</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05318</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.878</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -889,24 +772,6 @@
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>17.43768</v>
-      </c>
-      <c r="D20" t="n">
-        <v>17.68814</v>
-      </c>
-      <c r="E20" t="n">
-        <v>17.12245</v>
-      </c>
-      <c r="F20" t="n">
-        <v>45.25723</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05343</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.92821</v>
-      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -962,28 +827,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.79376</v>
+        <v>0.77116</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08563</v>
+        <v>0.08538999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.64451</v>
+        <v>0.63584</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9830100000000001</v>
+        <v>1.01846</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11679</v>
+        <v>0.11707</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00809</v>
+        <v>0.00773</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09692000000000001</v>
+        <v>0.09791999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.13013</v>
+        <v>0.13017</v>
       </c>
     </row>
     <row r="23">
@@ -993,28 +858,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.78592</v>
+        <v>0.78992</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08432000000000001</v>
+        <v>0.08434999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.62853</v>
+        <v>0.64458</v>
       </c>
       <c r="F23" t="n">
-        <v>0.99236</v>
+        <v>1.01799</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11454</v>
+        <v>0.11371</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00809</v>
+        <v>0.007820000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09757</v>
+        <v>0.09826</v>
       </c>
       <c r="J23" t="n">
-        <v>0.13409</v>
+        <v>0.13312</v>
       </c>
     </row>
     <row r="24">
@@ -1024,28 +889,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.79111</v>
+        <v>0.78771</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08467</v>
+        <v>0.08441</v>
       </c>
       <c r="E24" t="n">
-        <v>0.63679</v>
+        <v>0.65728</v>
       </c>
       <c r="F24" t="n">
-        <v>1.02418</v>
+        <v>1.01824</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11402</v>
+        <v>0.11571</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00801</v>
+        <v>0.007939999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09519</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.13196</v>
+        <v>0.13361</v>
       </c>
     </row>
     <row r="25">
@@ -1055,28 +920,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.77891</v>
+        <v>0.79634</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08422</v>
+        <v>0.08551</v>
       </c>
       <c r="E25" t="n">
-        <v>0.63353</v>
+        <v>0.63934</v>
       </c>
       <c r="F25" t="n">
-        <v>1.01854</v>
+        <v>0.99046</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11359</v>
+        <v>0.11476</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0081</v>
+        <v>0.00796</v>
       </c>
       <c r="I25" t="n">
-        <v>0.10017</v>
+        <v>0.09830999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.13194</v>
+        <v>0.13523</v>
       </c>
     </row>
     <row r="26">
@@ -1086,28 +951,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.77737</v>
+        <v>0.77766</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08538</v>
+        <v>0.08499</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6287</v>
+        <v>0.63476</v>
       </c>
       <c r="F26" t="n">
-        <v>0.99113</v>
+        <v>1.01792</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1119</v>
+        <v>0.11279</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00801</v>
+        <v>0.00796</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09873</v>
+        <v>0.09680999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.13184</v>
+        <v>0.1339</v>
       </c>
     </row>
     <row r="27">
@@ -1117,28 +982,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.78489</v>
+        <v>0.79408</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08508</v>
+        <v>0.08669</v>
       </c>
       <c r="E27" t="n">
-        <v>0.62648</v>
+        <v>0.64593</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0073</v>
+        <v>1.01811</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11399</v>
+        <v>0.11424</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00796</v>
+        <v>0.00809</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09823</v>
+        <v>0.09785000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>0.13214</v>
+        <v>0.13042</v>
       </c>
     </row>
     <row r="28">
@@ -1148,28 +1013,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.78705</v>
+        <v>0.77734</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08641</v>
+        <v>0.08628</v>
       </c>
       <c r="E28" t="n">
-        <v>0.63108</v>
+        <v>0.62263</v>
       </c>
       <c r="F28" t="n">
-        <v>1.02632</v>
+        <v>1.02368</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11615</v>
+        <v>0.11541</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00813</v>
+        <v>0.008030000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0973</v>
+        <v>0.09868</v>
       </c>
       <c r="J28" t="n">
-        <v>0.13096</v>
+        <v>0.13379</v>
       </c>
     </row>
     <row r="29">
@@ -1179,28 +1044,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.79104</v>
+        <v>0.79489</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0854</v>
+        <v>0.08278000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.63219</v>
+        <v>0.64886</v>
       </c>
       <c r="F29" t="n">
-        <v>0.98675</v>
+        <v>1.02526</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11023</v>
+        <v>0.11377</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00788</v>
+        <v>0.00781</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09747</v>
+        <v>0.09771000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.13477</v>
+        <v>0.13174</v>
       </c>
     </row>
     <row r="30">
@@ -1210,28 +1075,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7809700000000001</v>
+        <v>0.77518</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08382000000000001</v>
+        <v>0.08357000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.64447</v>
+        <v>0.63633</v>
       </c>
       <c r="F30" t="n">
-        <v>0.99116</v>
+        <v>1.02532</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11631</v>
+        <v>0.11454</v>
       </c>
       <c r="H30" t="n">
-        <v>0.008</v>
+        <v>0.00805</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09879</v>
+        <v>0.09835000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0.13243</v>
+        <v>0.13229</v>
       </c>
     </row>
   </sheetData>
